--- a/part 1.xlsx
+++ b/part 1.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hkmccloud-my.sharepoint.com/personal/yeo19_hyundai_com/Documents/업무/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{50B47978-6339-4B3E-8859-401D644D4F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0364B49E-216E-4E6E-BA62-060DE652BADF}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{50B47978-6339-4B3E-8859-401D644D4F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A292F56-E3BD-41AE-AB2A-7060E30347BA}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F99FC48C-34FE-434E-80D7-4E5AAE265EBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$849:$B$855</definedName>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="2083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="1940">
   <si>
     <t>자재번호</t>
   </si>
@@ -5857,10 +5856,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>임시1 4단 2열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>12230-05161</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5869,477 +5864,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>14720-13006B</t>
-  </si>
-  <si>
-    <t>BT</t>
-  </si>
-  <si>
-    <t>17993-19000</t>
-  </si>
-  <si>
-    <t>CP</t>
-  </si>
-  <si>
-    <t>17993-13000</t>
-  </si>
-  <si>
-    <t>BS</t>
-  </si>
-  <si>
-    <t>BH</t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>17303-35010</t>
-  </si>
-  <si>
-    <t>17308-79110</t>
-  </si>
-  <si>
-    <t>14720-15006B</t>
-  </si>
-  <si>
-    <t>14720-28003</t>
-  </si>
-  <si>
-    <t>14913-05000</t>
-  </si>
-  <si>
-    <t>CL</t>
-  </si>
-  <si>
-    <t>CG</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>14833-14141</t>
-  </si>
-  <si>
-    <t>17313-35000</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>17993-16000</t>
-  </si>
-  <si>
-    <t>14813-20239</t>
-  </si>
-  <si>
-    <t>17993-35000</t>
-  </si>
-  <si>
-    <t>CM</t>
-  </si>
-  <si>
-    <t>21811-7M500</t>
-  </si>
-  <si>
-    <t>BB</t>
-  </si>
-  <si>
-    <t>21813-7K600</t>
-  </si>
-  <si>
-    <t>21825-7D100</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>21825-7F300</t>
-  </si>
-  <si>
-    <t>21890-8D000</t>
-  </si>
-  <si>
-    <t>21895-8K000</t>
-  </si>
-  <si>
-    <t>CQ</t>
-  </si>
-  <si>
-    <t>28681-81001</t>
-  </si>
-  <si>
-    <t>28683-81001</t>
-  </si>
-  <si>
-    <t>28760-7P800</t>
-  </si>
-  <si>
-    <t>32710-8R001</t>
-  </si>
-  <si>
-    <t>43613-7R000</t>
-  </si>
-  <si>
-    <t>43613-7R020</t>
-  </si>
-  <si>
-    <t>43613-7R040</t>
-  </si>
-  <si>
-    <t>43711-8D001</t>
-  </si>
-  <si>
-    <t>52986-7F641</t>
-  </si>
-  <si>
-    <t>54324-67001</t>
-  </si>
-  <si>
-    <t>54325-67001</t>
-  </si>
-  <si>
-    <t>54753-7F300</t>
-  </si>
-  <si>
-    <t>55358-7P000</t>
-  </si>
-  <si>
-    <t>55359-7D000</t>
-  </si>
-  <si>
-    <t>55369-7R000</t>
-  </si>
-  <si>
-    <t>55553-7D500</t>
-  </si>
-  <si>
-    <t>55562-7D000</t>
-  </si>
-  <si>
-    <t>55877-7H550</t>
-  </si>
-  <si>
-    <t>55993-7N010</t>
-  </si>
-  <si>
-    <t>56334-69000</t>
-  </si>
-  <si>
-    <t>56335-8A100</t>
-  </si>
-  <si>
-    <t>56414-7R001</t>
-  </si>
-  <si>
-    <t>57580-8D101</t>
-  </si>
-  <si>
-    <t>57580-8D201</t>
-  </si>
-  <si>
-    <t>57681-67000</t>
-  </si>
-  <si>
-    <t>57682-8K180</t>
-  </si>
-  <si>
-    <t>57691-69001</t>
-  </si>
-  <si>
-    <t>58501-57001</t>
-  </si>
-  <si>
-    <t>58806-7X800</t>
-  </si>
-  <si>
-    <t>BK</t>
-  </si>
-  <si>
-    <t>58810-7X700</t>
-  </si>
-  <si>
-    <t>58810-7X800</t>
-  </si>
-  <si>
-    <t>58812-7X800</t>
-  </si>
-  <si>
-    <t>58912-7X900</t>
-  </si>
-  <si>
-    <t>58912-7X930</t>
-  </si>
-  <si>
-    <t>58914-7X900</t>
-  </si>
-  <si>
-    <t>58914-7X910</t>
-  </si>
-  <si>
-    <t>58914-7X920</t>
-  </si>
-  <si>
-    <t>58916-7X900</t>
-  </si>
-  <si>
-    <t>58922-7X920</t>
-  </si>
-  <si>
-    <t>58932-7X900</t>
-  </si>
-  <si>
-    <t>58932-7X920</t>
-  </si>
-  <si>
-    <t>58942-7N000</t>
-  </si>
-  <si>
-    <t>58942-88500</t>
-  </si>
-  <si>
-    <t>58952-7X910</t>
-  </si>
-  <si>
-    <t>58952-7X920</t>
-  </si>
-  <si>
-    <t>58953-7X950</t>
-  </si>
-  <si>
-    <t>58954-7X920</t>
-  </si>
-  <si>
-    <t>58954-7X930</t>
-  </si>
-  <si>
-    <t>64401-8C000</t>
-  </si>
-  <si>
-    <t>64403-8C000</t>
-  </si>
-  <si>
-    <t>81199-38000</t>
-  </si>
-  <si>
-    <t>81919-11400</t>
-  </si>
-  <si>
-    <t>82412-23000</t>
-  </si>
-  <si>
-    <t>82740-7A000</t>
-  </si>
-  <si>
-    <t>82777-7A000</t>
-  </si>
-  <si>
-    <t>91191-71000</t>
-  </si>
-  <si>
-    <t>91421-4A000</t>
-  </si>
-  <si>
-    <t>91421-5H000</t>
-  </si>
-  <si>
-    <t>91590-6A001</t>
-  </si>
-  <si>
-    <t>91590-6A011</t>
-  </si>
-  <si>
-    <t>91590-6A021</t>
-  </si>
-  <si>
-    <t>91590-6A031</t>
-  </si>
-  <si>
-    <t>91590-6A041</t>
-  </si>
-  <si>
-    <t>91590-6A051</t>
-  </si>
-  <si>
-    <t>91590-6A061</t>
-  </si>
-  <si>
-    <t>91590-6A071</t>
-  </si>
-  <si>
-    <t>91590-6A081</t>
-  </si>
-  <si>
-    <t>91590-6A121</t>
-  </si>
-  <si>
-    <t>91590-6A131</t>
-  </si>
-  <si>
-    <t>91596-7S300</t>
-  </si>
-  <si>
-    <t>91596-7S350</t>
-  </si>
-  <si>
-    <t>93283-73001</t>
-  </si>
-  <si>
-    <t>94471-8D000</t>
-  </si>
-  <si>
-    <t>95225-7A500</t>
-  </si>
-  <si>
-    <t>96810-7C000</t>
-  </si>
-  <si>
-    <t>99187-8K350</t>
-  </si>
-  <si>
-    <t>99187-8K400</t>
-  </si>
-  <si>
-    <t>BB, BL</t>
-  </si>
-  <si>
-    <t>BS, BT, CP</t>
-  </si>
-  <si>
-    <t>BB, CQ</t>
-  </si>
-  <si>
-    <t>BB, CP</t>
-  </si>
-  <si>
-    <t>BB, BC, BT</t>
-  </si>
-  <si>
-    <t>BM, CL</t>
-  </si>
-  <si>
-    <t>BB, BC, BL</t>
-  </si>
-  <si>
-    <t>BB, BC</t>
-  </si>
-  <si>
-    <t>BB, BC, BM</t>
-  </si>
-  <si>
-    <t>CN, CQ</t>
-  </si>
-  <si>
-    <t>BM, BS, BT</t>
-  </si>
-  <si>
-    <t>BH, BS, BT</t>
-  </si>
-  <si>
-    <t>BH, BS, CP</t>
-  </si>
-  <si>
-    <t>BB, BC, BS, BT</t>
-  </si>
-  <si>
-    <t>CK, CN</t>
-  </si>
-  <si>
-    <t>BH, BM, BS, CG</t>
-  </si>
-  <si>
-    <t>BB, BC, BS</t>
-  </si>
-  <si>
-    <t>BH, BM, BS, BT, CQ</t>
-  </si>
-  <si>
-    <t>BB, BC, BH, BS</t>
-  </si>
-  <si>
-    <t>BH, BM, BS</t>
-  </si>
-  <si>
-    <t>BH, BM, CG</t>
-  </si>
-  <si>
-    <t>AG, BG, BH, BS, BT, CE</t>
-  </si>
-  <si>
-    <t>AG, BH, BS</t>
-  </si>
-  <si>
-    <t>BM, BS</t>
-  </si>
-  <si>
-    <t>BB, BC, BH, BM, BS</t>
-  </si>
-  <si>
-    <t>BM, BS, CM, CN</t>
-  </si>
-  <si>
-    <t>BM, BS, BT, CE, CM, CN, CQ, CR</t>
-  </si>
-  <si>
-    <t>BS, CG</t>
-  </si>
-  <si>
-    <t>CE, CL</t>
-  </si>
-  <si>
-    <t>BS, CR, T2</t>
-  </si>
-  <si>
-    <t>BM, BS, CB, CE, CG, CK, CL</t>
-  </si>
-  <si>
-    <t>BG, BH, BS, BT, CL, CN, CP, CQ, CR</t>
-  </si>
-  <si>
-    <t>BB, BS, BT, CL, CP</t>
-  </si>
-  <si>
-    <t>BB, BS, BT, CP</t>
-  </si>
-  <si>
-    <t>BS, CL, CN, CP</t>
-  </si>
-  <si>
-    <t>BB, BS, CE, CG, CL, CN, CP</t>
-  </si>
-  <si>
-    <t>BS, BT, CG, CL, CN, CP, CR</t>
-  </si>
-  <si>
-    <t>BB, BS, BT, CB, CE, CO, CP, CQ, CR</t>
-  </si>
-  <si>
-    <t>BB, BH, BT, CG, CN, CP, CR</t>
-  </si>
-  <si>
-    <t>CB, CG, CP, CR</t>
-  </si>
-  <si>
-    <t>BH, BS</t>
-  </si>
-  <si>
-    <t>BH, CG, CP</t>
-  </si>
-  <si>
-    <t>BB, BH, BS, BT, CE, CN, CP, CR</t>
-  </si>
-  <si>
-    <t>BB, BC, BS, BT, CE, CN, CO, CP, CR</t>
-  </si>
-  <si>
-    <t>BB, CO</t>
-  </si>
-  <si>
-    <t>BB, CE, CG, CO, CR</t>
-  </si>
-  <si>
-    <t>BS, BT, CR</t>
-  </si>
-  <si>
     <t>12414-04203</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6348,14 +5872,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>임시1 6단 1열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>임시1 6단 2열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11230-06123</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6368,15 +5884,78 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3-3 6단 4열</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11415-06356B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3-3 4단 1열</t>
+    <t>11203-06401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11995-14507</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12414-04303</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12414-04353</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13387-06007B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12293-06253</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임시1 4단2열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임시1 6단1열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임시1 6단2열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-3 6단4열</t>
+  </si>
+  <si>
+    <t>3-3 4단1열</t>
+  </si>
+  <si>
+    <t>2-8 5단2열</t>
+  </si>
+  <si>
+    <t>3-3 5단1열</t>
+  </si>
+  <si>
+    <t>임시1 5단1열</t>
+  </si>
+  <si>
+    <t>3-3 5단4열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-3 5단2열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-3 5단6열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11253-06201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-3 4단6열</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6484,7 +6063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6521,14 +6100,18 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6869,7 +6452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD56D84-AAB8-4F28-8C6E-523199CE1743}">
-  <dimension ref="A1:G963"/>
+  <dimension ref="A1:G970"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
@@ -11358,7 +10941,7 @@
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B561" s="3" t="s">
         <v>1454</v>
@@ -11942,7 +11525,7 @@
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634" s="3" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B634" s="3" t="s">
         <v>1527</v>
@@ -14538,1708 +14121,116 @@
         <v>1912</v>
       </c>
       <c r="B958" s="3" t="s">
-        <v>1913</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="959" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A959" s="11" t="s">
-        <v>2073</v>
+        <v>1915</v>
       </c>
       <c r="B959" s="11" t="s">
-        <v>2075</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="960" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A960" s="11" t="s">
-        <v>2074</v>
+        <v>1916</v>
       </c>
       <c r="B960" s="11" t="s">
-        <v>2076</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A961" s="3" t="s">
-        <v>2077</v>
+        <v>1917</v>
       </c>
       <c r="B961" s="3" t="s">
-        <v>2078</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A962" s="3" t="s">
-        <v>2079</v>
+        <v>1919</v>
       </c>
       <c r="B962" s="3" t="s">
-        <v>2080</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A963" s="12" t="s">
-        <v>2081</v>
+      <c r="A963" s="3" t="s">
+        <v>1920</v>
       </c>
       <c r="B963" s="3" t="s">
-        <v>2082</v>
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A964" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B964" s="3" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A965" s="3" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B965" s="3" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="966" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A966" s="3" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B966" s="3" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A967" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B967" s="3" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="968" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A968" s="3" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B968" s="3" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="969" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A969" s="3" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B969" s="3" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A970" s="3" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B970" s="3" t="s">
+        <v>1939</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A864:B943 A1 A2:B846 A847:A848 A944:A963">
-    <cfRule type="duplicateValues" dxfId="0" priority="6" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A864:B943 A1 A2:B846 A847:A848 A944:A970">
+    <cfRule type="duplicateValues" dxfId="1" priority="7" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 본 문서는 현대자동차·기아의 정보자산으로 귀사와의 비밀유지계약 및 제반법률에 따라 법적 보호를 받습니다.</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BEFAF9-5EF7-4431-AC05-9AB822012ED5}">
-  <dimension ref="A1:H83"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1939</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2026</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1939</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1941</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2026</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1941</v>
-      </c>
-      <c r="H2" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1942</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1942</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1944</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2027</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1944</v>
-      </c>
-      <c r="H4" t="s">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1945</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1940</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1945</v>
-      </c>
-      <c r="H5" t="s">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1923</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1946</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2028</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1946</v>
-      </c>
-      <c r="H6" t="s">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1948</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1940</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1948</v>
-      </c>
-      <c r="H7" t="s">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1924</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1949</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2029</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1949</v>
-      </c>
-      <c r="H8" t="s">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1950</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2030</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1950</v>
-      </c>
-      <c r="H9" t="s">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1951</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1921</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1951</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>1926</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1952</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1952</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1953</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1953</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1954</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1954</v>
-      </c>
-      <c r="H13" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1955</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1947</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1955</v>
-      </c>
-      <c r="H14" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1956</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2031</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1956</v>
-      </c>
-      <c r="H15" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1957</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1917</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1957</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1958</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1917</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1958</v>
-      </c>
-      <c r="H17" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1959</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1917</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1959</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E19" t="s">
-        <v>2032</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1960</v>
-      </c>
-      <c r="H19" t="s">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1961</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2033</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1961</v>
-      </c>
-      <c r="H20" t="s">
-        <v>2033</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>1924</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1962</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2034</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1962</v>
-      </c>
-      <c r="H21" t="s">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1963</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1917</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1963</v>
-      </c>
-      <c r="H22" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>1932</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1964</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1917</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1964</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1965</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1917</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1965</v>
-      </c>
-      <c r="H24" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1966</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1921</v>
-      </c>
-      <c r="G25" t="s">
-        <v>1966</v>
-      </c>
-      <c r="H25" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1967</v>
-      </c>
-      <c r="E26" t="s">
-        <v>2035</v>
-      </c>
-      <c r="G26" t="s">
-        <v>1967</v>
-      </c>
-      <c r="H26" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1968</v>
-      </c>
-      <c r="E27" t="s">
-        <v>2035</v>
-      </c>
-      <c r="G27" t="s">
-        <v>1968</v>
-      </c>
-      <c r="H27" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1969</v>
-      </c>
-      <c r="E28" t="s">
-        <v>2036</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1969</v>
-      </c>
-      <c r="H28" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>323</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1934</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1970</v>
-      </c>
-      <c r="E29" t="s">
-        <v>2037</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1970</v>
-      </c>
-      <c r="H29" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1971</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2038</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1971</v>
-      </c>
-      <c r="H30" t="s">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1972</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1921</v>
-      </c>
-      <c r="G31" t="s">
-        <v>1972</v>
-      </c>
-      <c r="H31" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1973</v>
-      </c>
-      <c r="E32" t="s">
-        <v>2039</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1973</v>
-      </c>
-      <c r="H32" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1917</v>
-      </c>
-      <c r="G33" t="s">
-        <v>1974</v>
-      </c>
-      <c r="H33" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1975</v>
-      </c>
-      <c r="E34" t="s">
-        <v>2040</v>
-      </c>
-      <c r="G34" t="s">
-        <v>1975</v>
-      </c>
-      <c r="H34" t="s">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1976</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1977</v>
-      </c>
-      <c r="G35" t="s">
-        <v>1976</v>
-      </c>
-      <c r="H35" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1978</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1977</v>
-      </c>
-      <c r="G36" t="s">
-        <v>1978</v>
-      </c>
-      <c r="H36" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>1932</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1979</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1977</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1979</v>
-      </c>
-      <c r="H37" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1980</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1977</v>
-      </c>
-      <c r="G38" t="s">
-        <v>1980</v>
-      </c>
-      <c r="H38" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1981</v>
-      </c>
-      <c r="E39" t="s">
-        <v>2041</v>
-      </c>
-      <c r="G39" t="s">
-        <v>1981</v>
-      </c>
-      <c r="H39" t="s">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1982</v>
-      </c>
-      <c r="E40" t="s">
-        <v>2042</v>
-      </c>
-      <c r="G40" t="s">
-        <v>1982</v>
-      </c>
-      <c r="H40" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D41" t="s">
-        <v>1983</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1940</v>
-      </c>
-      <c r="G41" t="s">
-        <v>1983</v>
-      </c>
-      <c r="H41" t="s">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1984</v>
-      </c>
-      <c r="E42" t="s">
-        <v>2043</v>
-      </c>
-      <c r="G42" t="s">
-        <v>1984</v>
-      </c>
-      <c r="H42" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1985</v>
-      </c>
-      <c r="E43" t="s">
-        <v>2044</v>
-      </c>
-      <c r="G43" t="s">
-        <v>1985</v>
-      </c>
-      <c r="H43" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D44" t="s">
-        <v>1986</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1921</v>
-      </c>
-      <c r="G44" t="s">
-        <v>1986</v>
-      </c>
-      <c r="H44" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1923</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1987</v>
-      </c>
-      <c r="E45" t="s">
-        <v>2045</v>
-      </c>
-      <c r="G45" t="s">
-        <v>1987</v>
-      </c>
-      <c r="H45" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>323</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1934</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1988</v>
-      </c>
-      <c r="E46" t="s">
-        <v>2044</v>
-      </c>
-      <c r="G46" t="s">
-        <v>1988</v>
-      </c>
-      <c r="H46" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>1926</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1989</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1921</v>
-      </c>
-      <c r="G47" t="s">
-        <v>1989</v>
-      </c>
-      <c r="H47" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1990</v>
-      </c>
-      <c r="E48" t="s">
-        <v>2046</v>
-      </c>
-      <c r="G48" t="s">
-        <v>1990</v>
-      </c>
-      <c r="H48" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1991</v>
-      </c>
-      <c r="E49" t="s">
-        <v>1917</v>
-      </c>
-      <c r="G49" t="s">
-        <v>1991</v>
-      </c>
-      <c r="H49" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1992</v>
-      </c>
-      <c r="E50" t="s">
-        <v>2047</v>
-      </c>
-      <c r="G50" t="s">
-        <v>1992</v>
-      </c>
-      <c r="H50" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>323</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1934</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1993</v>
-      </c>
-      <c r="E51" t="s">
-        <v>2048</v>
-      </c>
-      <c r="G51" t="s">
-        <v>1993</v>
-      </c>
-      <c r="H51" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>1937</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1994</v>
-      </c>
-      <c r="E52" t="s">
-        <v>1922</v>
-      </c>
-      <c r="G52" t="s">
-        <v>1994</v>
-      </c>
-      <c r="H52" t="s">
-        <v>1922</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1995</v>
-      </c>
-      <c r="E53" t="s">
-        <v>2049</v>
-      </c>
-      <c r="G53" t="s">
-        <v>1995</v>
-      </c>
-      <c r="H53" t="s">
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1996</v>
-      </c>
-      <c r="E54" t="s">
-        <v>2050</v>
-      </c>
-      <c r="G54" t="s">
-        <v>1996</v>
-      </c>
-      <c r="H54" t="s">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>1926</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1997</v>
-      </c>
-      <c r="E55" t="s">
-        <v>2051</v>
-      </c>
-      <c r="G55" t="s">
-        <v>1997</v>
-      </c>
-      <c r="H55" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D56" t="s">
-        <v>1998</v>
-      </c>
-      <c r="E56" t="s">
-        <v>2052</v>
-      </c>
-      <c r="G56" t="s">
-        <v>1998</v>
-      </c>
-      <c r="H56" t="s">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D57" t="s">
-        <v>1999</v>
-      </c>
-      <c r="E57" t="s">
-        <v>2053</v>
-      </c>
-      <c r="G57" t="s">
-        <v>1999</v>
-      </c>
-      <c r="H57" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>299</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1934</v>
-      </c>
-      <c r="D58" t="s">
-        <v>2000</v>
-      </c>
-      <c r="E58" t="s">
-        <v>2054</v>
-      </c>
-      <c r="G58" t="s">
-        <v>2000</v>
-      </c>
-      <c r="H58" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D59" t="s">
-        <v>2001</v>
-      </c>
-      <c r="E59" t="s">
-        <v>1947</v>
-      </c>
-      <c r="G59" t="s">
-        <v>2001</v>
-      </c>
-      <c r="H59" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D60" t="s">
-        <v>2002</v>
-      </c>
-      <c r="E60" t="s">
-        <v>2055</v>
-      </c>
-      <c r="G60" t="s">
-        <v>2002</v>
-      </c>
-      <c r="H60" t="s">
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>323</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1934</v>
-      </c>
-      <c r="D61" t="s">
-        <v>2003</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1947</v>
-      </c>
-      <c r="G61" t="s">
-        <v>2003</v>
-      </c>
-      <c r="H61" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>1932</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D62" t="s">
-        <v>2004</v>
-      </c>
-      <c r="E62" t="s">
-        <v>2056</v>
-      </c>
-      <c r="G62" t="s">
-        <v>2004</v>
-      </c>
-      <c r="H62" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D63" t="s">
-        <v>2005</v>
-      </c>
-      <c r="E63" t="s">
-        <v>1947</v>
-      </c>
-      <c r="G63" t="s">
-        <v>2005</v>
-      </c>
-      <c r="H63" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D64" t="s">
-        <v>2006</v>
-      </c>
-      <c r="E64" t="s">
-        <v>2057</v>
-      </c>
-      <c r="G64" t="s">
-        <v>2006</v>
-      </c>
-      <c r="H64" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D65" t="s">
-        <v>2007</v>
-      </c>
-      <c r="E65" t="s">
-        <v>2058</v>
-      </c>
-      <c r="G65" t="s">
-        <v>2007</v>
-      </c>
-      <c r="H65" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D66" t="s">
-        <v>2008</v>
-      </c>
-      <c r="E66" t="s">
-        <v>2059</v>
-      </c>
-      <c r="G66" t="s">
-        <v>2008</v>
-      </c>
-      <c r="H66" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D67" t="s">
-        <v>2009</v>
-      </c>
-      <c r="E67" t="s">
-        <v>2060</v>
-      </c>
-      <c r="G67" t="s">
-        <v>2009</v>
-      </c>
-      <c r="H67" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D68" t="s">
-        <v>2010</v>
-      </c>
-      <c r="E68" t="s">
-        <v>2061</v>
-      </c>
-      <c r="G68" t="s">
-        <v>2010</v>
-      </c>
-      <c r="H68" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1938</v>
-      </c>
-      <c r="D69" t="s">
-        <v>2011</v>
-      </c>
-      <c r="E69" t="s">
-        <v>2062</v>
-      </c>
-      <c r="G69" t="s">
-        <v>2011</v>
-      </c>
-      <c r="H69" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D70" t="s">
-        <v>2012</v>
-      </c>
-      <c r="E70" t="s">
-        <v>2063</v>
-      </c>
-      <c r="G70" t="s">
-        <v>2012</v>
-      </c>
-      <c r="H70" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>300</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1934</v>
-      </c>
-      <c r="D71" t="s">
-        <v>2013</v>
-      </c>
-      <c r="E71" t="s">
-        <v>2058</v>
-      </c>
-      <c r="G71" t="s">
-        <v>2013</v>
-      </c>
-      <c r="H71" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D72" t="s">
-        <v>2014</v>
-      </c>
-      <c r="E72" t="s">
-        <v>2064</v>
-      </c>
-      <c r="G72" t="s">
-        <v>2014</v>
-      </c>
-      <c r="H72" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D73" t="s">
-        <v>2015</v>
-      </c>
-      <c r="E73" t="s">
-        <v>2065</v>
-      </c>
-      <c r="G73" t="s">
-        <v>2015</v>
-      </c>
-      <c r="H73" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D74" t="s">
-        <v>2016</v>
-      </c>
-      <c r="E74" t="s">
-        <v>2066</v>
-      </c>
-      <c r="G74" t="s">
-        <v>2016</v>
-      </c>
-      <c r="H74" t="s">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D75" t="s">
-        <v>2017</v>
-      </c>
-      <c r="E75" t="s">
-        <v>2067</v>
-      </c>
-      <c r="G75" t="s">
-        <v>2017</v>
-      </c>
-      <c r="H75" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1917</v>
-      </c>
-      <c r="D76" t="s">
-        <v>2018</v>
-      </c>
-      <c r="E76" t="s">
-        <v>2068</v>
-      </c>
-      <c r="G76" t="s">
-        <v>2018</v>
-      </c>
-      <c r="H76" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D77" t="s">
-        <v>2019</v>
-      </c>
-      <c r="E77" t="s">
-        <v>2069</v>
-      </c>
-      <c r="G77" t="s">
-        <v>2019</v>
-      </c>
-      <c r="H77" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D78" t="s">
-        <v>2020</v>
-      </c>
-      <c r="E78" t="s">
-        <v>2070</v>
-      </c>
-      <c r="G78" t="s">
-        <v>2020</v>
-      </c>
-      <c r="H78" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D79" t="s">
-        <v>2021</v>
-      </c>
-      <c r="E79" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G79" t="s">
-        <v>2021</v>
-      </c>
-      <c r="H79" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D80" t="s">
-        <v>2022</v>
-      </c>
-      <c r="E80" t="s">
-        <v>2071</v>
-      </c>
-      <c r="G80" t="s">
-        <v>2022</v>
-      </c>
-      <c r="H80" t="s">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="81" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D81" t="s">
-        <v>2023</v>
-      </c>
-      <c r="E81" t="s">
-        <v>2072</v>
-      </c>
-      <c r="G81" t="s">
-        <v>2023</v>
-      </c>
-      <c r="H81" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="82" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D82" t="s">
-        <v>2024</v>
-      </c>
-      <c r="E82" t="s">
-        <v>2037</v>
-      </c>
-      <c r="G82" t="s">
-        <v>2024</v>
-      </c>
-      <c r="H82" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="83" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D83" t="s">
-        <v>2025</v>
-      </c>
-      <c r="E83" t="s">
-        <v>2036</v>
-      </c>
-      <c r="G83" t="s">
-        <v>2025</v>
-      </c>
-      <c r="H83" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>